--- a/BWI/bestwine_output/bestwine_Taiwan.xlsx
+++ b/BWI/bestwine_output/bestwine_Taiwan.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA177"/>
+  <dimension ref="A1:AA178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -18806,6 +18806,107 @@
         </is>
       </c>
     </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Leading Brands Wines &amp; Spirits Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Leading Brands Wines &amp; Spirits Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>13568</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>Taipei City, Zhongshan District</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>58 Section 3, Minquan East Road, Section 3</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>10491</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>http://www.leading-brands.com.tw</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr"/>
+      <c r="K178" s="2" t="inlineStr"/>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr"/>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>order@leading-brands.com.tw</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 2507 2558</t>
+        </is>
+      </c>
+      <c r="P178" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q178" s="2" t="inlineStr">
+        <is>
+          <t>27341945</t>
+        </is>
+      </c>
+      <c r="R178" s="2" t="inlineStr"/>
+      <c r="S178" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LeadingBrandsWineSpirits</t>
+        </is>
+      </c>
+      <c r="T178" s="2" t="inlineStr"/>
+      <c r="U178" s="2" t="inlineStr"/>
+      <c r="V178" s="2" t="inlineStr"/>
+      <c r="W178" s="2" t="inlineStr">
+        <is>
+          <t>Huang Sammy</t>
+        </is>
+      </c>
+      <c r="X178" s="2" t="inlineStr">
+        <is>
+          <t>Import Division</t>
+        </is>
+      </c>
+      <c r="Y178" s="2" t="inlineStr"/>
+      <c r="Z178" s="2" t="inlineStr"/>
+      <c r="AA178" s="2" t="inlineStr">
+        <is>
+          <t>https://tw.linkedin.com/pub/huang-sammy/34/107/983/en</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Taiwan.xlsx
+++ b/BWI/bestwine_output/bestwine_Taiwan.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA178"/>
+  <dimension ref="A1:AA181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -18907,6 +18907,269 @@
         </is>
       </c>
     </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>Three Merchants Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>Three Merchants Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>89394</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>Chengdu Shi</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>Taipei City, Zhongshan District</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>4 Section 3, Minquan East Road</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>10491</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.simplemart.com.tw</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr"/>
+      <c r="K179" s="2" t="inlineStr"/>
+      <c r="L179" s="2" t="inlineStr"/>
+      <c r="M179" s="2" t="inlineStr"/>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>webservice@simplemart.com.tw</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>+886 80 042 6666</t>
+        </is>
+      </c>
+      <c r="P179" s="2" t="inlineStr"/>
+      <c r="Q179" s="2" t="inlineStr"/>
+      <c r="R179" s="2" t="inlineStr"/>
+      <c r="S179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/simplemart1/</t>
+        </is>
+      </c>
+      <c r="T179" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/simplemarttw</t>
+        </is>
+      </c>
+      <c r="U179" s="2" t="inlineStr"/>
+      <c r="V179" s="2" t="inlineStr"/>
+      <c r="W179" s="2" t="inlineStr"/>
+      <c r="X179" s="2" t="inlineStr"/>
+      <c r="Y179" s="2" t="inlineStr"/>
+      <c r="Z179" s="2" t="inlineStr"/>
+      <c r="AA179" s="2" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>Winedup Taiwan</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>Winedup Taiwan</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>122525</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>Taichung</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>Taichung City, Nantun District</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>519 Yongchun East 7th Road</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>https://winedup.com.tw</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr"/>
+      <c r="K180" s="2" t="inlineStr"/>
+      <c r="L180" s="2" t="inlineStr"/>
+      <c r="M180" s="2" t="inlineStr"/>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>winedup519@gmail.com</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>+886 4 2380 4335</t>
+        </is>
+      </c>
+      <c r="P180" s="2" t="inlineStr"/>
+      <c r="Q180" s="2" t="inlineStr"/>
+      <c r="R180" s="2" t="inlineStr"/>
+      <c r="S180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WinedUp.tw/</t>
+        </is>
+      </c>
+      <c r="T180" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winedup.tw/</t>
+        </is>
+      </c>
+      <c r="U180" s="2" t="inlineStr"/>
+      <c r="V180" s="2" t="inlineStr"/>
+      <c r="W180" s="2" t="inlineStr"/>
+      <c r="X180" s="2" t="inlineStr"/>
+      <c r="Y180" s="2" t="inlineStr"/>
+      <c r="Z180" s="2" t="inlineStr"/>
+      <c r="AA180" s="2" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>Leading Brands Wines &amp; Spirits Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>Leading Brands Wines &amp; Spirits Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>13568</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>Taipei City, Zhongshan District</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>58 Section 3, Minquan East Road, Section 3</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>10491</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>http://www.leading-brands.com.tw</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr"/>
+      <c r="K181" s="2" t="inlineStr"/>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr"/>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>order@leading-brands.com.tw</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 2507 2558</t>
+        </is>
+      </c>
+      <c r="P181" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q181" s="2" t="inlineStr">
+        <is>
+          <t>27341945</t>
+        </is>
+      </c>
+      <c r="R181" s="2" t="inlineStr"/>
+      <c r="S181" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LeadingBrandsWineSpirits</t>
+        </is>
+      </c>
+      <c r="T181" s="2" t="inlineStr"/>
+      <c r="U181" s="2" t="inlineStr"/>
+      <c r="V181" s="2" t="inlineStr"/>
+      <c r="W181" s="2" t="inlineStr">
+        <is>
+          <t>Huang Sammy</t>
+        </is>
+      </c>
+      <c r="X181" s="2" t="inlineStr">
+        <is>
+          <t>Import Division</t>
+        </is>
+      </c>
+      <c r="Y181" s="2" t="inlineStr"/>
+      <c r="Z181" s="2" t="inlineStr"/>
+      <c r="AA181" s="2" t="inlineStr">
+        <is>
+          <t>https://tw.linkedin.com/pub/huang-sammy/34/107/983/en</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Taiwan.xlsx
+++ b/BWI/bestwine_output/bestwine_Taiwan.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA181"/>
+  <dimension ref="A1:AA187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -19170,6 +19170,552 @@
         </is>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>Jifu International Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>Jifu International Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>79089</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>Taipei, Da’an District</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>69-6 Section 4, Zhongxiao East Road</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>https://hungarywine.com.tw</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr"/>
+      <c r="K182" s="2" t="inlineStr"/>
+      <c r="L182" s="2" t="inlineStr"/>
+      <c r="M182" s="2" t="inlineStr"/>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>info@chifuinternational.com</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 2731 0829</t>
+        </is>
+      </c>
+      <c r="P182" s="2" t="inlineStr"/>
+      <c r="Q182" s="2" t="inlineStr"/>
+      <c r="R182" s="2" t="inlineStr"/>
+      <c r="S182" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/chifuwine/</t>
+        </is>
+      </c>
+      <c r="T182" s="2" t="inlineStr"/>
+      <c r="U182" s="2" t="inlineStr"/>
+      <c r="V182" s="2" t="inlineStr"/>
+      <c r="W182" s="2" t="inlineStr"/>
+      <c r="X182" s="2" t="inlineStr"/>
+      <c r="Y182" s="2" t="inlineStr"/>
+      <c r="Z182" s="2" t="inlineStr"/>
+      <c r="AA182" s="2" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>Dixitwine Shuo Wine Trading Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>Dixitwine Shuo Wine Trading Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>79082</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
+        <is>
+          <t>New Taipei City</t>
+        </is>
+      </c>
+      <c r="F183" s="2" t="inlineStr"/>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>14F-10, No. 95, Section 1, Xintai 5th Road, Xizhi District</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dixitwine.com</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr"/>
+      <c r="K183" s="2" t="inlineStr"/>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr"/>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>info@dixitwine.com</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 2552 8690</t>
+        </is>
+      </c>
+      <c r="P183" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q183" s="2" t="inlineStr">
+        <is>
+          <t>43943711</t>
+        </is>
+      </c>
+      <c r="R183" s="2" t="inlineStr"/>
+      <c r="S183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/911-Wine-Club-101431671228109/</t>
+        </is>
+      </c>
+      <c r="T183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/911_wine_club/</t>
+        </is>
+      </c>
+      <c r="U183" s="2" t="inlineStr"/>
+      <c r="V183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCmU3F2DYY5gtc5yb9JnRFfg</t>
+        </is>
+      </c>
+      <c r="W183" s="2" t="inlineStr">
+        <is>
+          <t>Elaine Lin</t>
+        </is>
+      </c>
+      <c r="X183" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Executive</t>
+        </is>
+      </c>
+      <c r="Y183" s="2" t="inlineStr"/>
+      <c r="Z183" s="2" t="inlineStr"/>
+      <c r="AA183" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elaine-lin-441b881a2/?originalSubdomain=tw</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
+        <is>
+          <t>Dixitwine Shuo Wine Trading Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>Dixitwine Shuo Wine Trading Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>79082</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E184" s="2" t="inlineStr">
+        <is>
+          <t>New Taipei City</t>
+        </is>
+      </c>
+      <c r="F184" s="2" t="inlineStr"/>
+      <c r="G184" s="2" t="inlineStr">
+        <is>
+          <t>14F-10, No. 95, Section 1, Xintai 5th Road, Xizhi District</t>
+        </is>
+      </c>
+      <c r="H184" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dixitwine.com</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="inlineStr"/>
+      <c r="K184" s="2" t="inlineStr"/>
+      <c r="L184" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M184" s="2" t="inlineStr"/>
+      <c r="N184" s="2" t="inlineStr">
+        <is>
+          <t>info@dixitwine.com</t>
+        </is>
+      </c>
+      <c r="O184" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 2552 8690</t>
+        </is>
+      </c>
+      <c r="P184" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q184" s="2" t="inlineStr">
+        <is>
+          <t>43943711</t>
+        </is>
+      </c>
+      <c r="R184" s="2" t="inlineStr"/>
+      <c r="S184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/911-Wine-Club-101431671228109/</t>
+        </is>
+      </c>
+      <c r="T184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/911_wine_club/</t>
+        </is>
+      </c>
+      <c r="U184" s="2" t="inlineStr"/>
+      <c r="V184" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCmU3F2DYY5gtc5yb9JnRFfg</t>
+        </is>
+      </c>
+      <c r="W184" s="2" t="inlineStr">
+        <is>
+          <t>Po-yu Chen</t>
+        </is>
+      </c>
+      <c r="X184" s="2" t="inlineStr">
+        <is>
+          <t>Founder And Executive Director</t>
+        </is>
+      </c>
+      <c r="Y184" s="2" t="inlineStr"/>
+      <c r="Z184" s="2" t="inlineStr"/>
+      <c r="AA184" s="2" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
+        <is>
+          <t>Three Merchants Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>Three Merchants Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>89394</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E185" s="2" t="inlineStr">
+        <is>
+          <t>Chengdu Shi</t>
+        </is>
+      </c>
+      <c r="F185" s="2" t="inlineStr">
+        <is>
+          <t>Taipei City, Zhongshan District</t>
+        </is>
+      </c>
+      <c r="G185" s="2" t="inlineStr">
+        <is>
+          <t>4 Section 3, Minquan East Road</t>
+        </is>
+      </c>
+      <c r="H185" s="2" t="inlineStr">
+        <is>
+          <t>10491</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.simplemart.com.tw</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="inlineStr"/>
+      <c r="K185" s="2" t="inlineStr"/>
+      <c r="L185" s="2" t="inlineStr"/>
+      <c r="M185" s="2" t="inlineStr"/>
+      <c r="N185" s="2" t="inlineStr">
+        <is>
+          <t>webservice@simplemart.com.tw</t>
+        </is>
+      </c>
+      <c r="O185" s="2" t="inlineStr">
+        <is>
+          <t>+886 80 042 6666</t>
+        </is>
+      </c>
+      <c r="P185" s="2" t="inlineStr"/>
+      <c r="Q185" s="2" t="inlineStr"/>
+      <c r="R185" s="2" t="inlineStr"/>
+      <c r="S185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/simplemart1/</t>
+        </is>
+      </c>
+      <c r="T185" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/simplemarttw</t>
+        </is>
+      </c>
+      <c r="U185" s="2" t="inlineStr"/>
+      <c r="V185" s="2" t="inlineStr"/>
+      <c r="W185" s="2" t="inlineStr"/>
+      <c r="X185" s="2" t="inlineStr"/>
+      <c r="Y185" s="2" t="inlineStr"/>
+      <c r="Z185" s="2" t="inlineStr"/>
+      <c r="AA185" s="2" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="inlineStr">
+        <is>
+          <t>Winedup Taiwan</t>
+        </is>
+      </c>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>Winedup Taiwan</t>
+        </is>
+      </c>
+      <c r="C186" s="2" t="inlineStr">
+        <is>
+          <t>122525</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E186" s="2" t="inlineStr">
+        <is>
+          <t>Taichung</t>
+        </is>
+      </c>
+      <c r="F186" s="2" t="inlineStr">
+        <is>
+          <t>Taichung City, Nantun District</t>
+        </is>
+      </c>
+      <c r="G186" s="2" t="inlineStr">
+        <is>
+          <t>519 Yongchun East 7th Road</t>
+        </is>
+      </c>
+      <c r="H186" s="2" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>https://winedup.com.tw</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr"/>
+      <c r="L186" s="2" t="inlineStr"/>
+      <c r="M186" s="2" t="inlineStr"/>
+      <c r="N186" s="2" t="inlineStr">
+        <is>
+          <t>winedup519@gmail.com</t>
+        </is>
+      </c>
+      <c r="O186" s="2" t="inlineStr">
+        <is>
+          <t>+886 4 2380 4335</t>
+        </is>
+      </c>
+      <c r="P186" s="2" t="inlineStr"/>
+      <c r="Q186" s="2" t="inlineStr"/>
+      <c r="R186" s="2" t="inlineStr"/>
+      <c r="S186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/WinedUp.tw/</t>
+        </is>
+      </c>
+      <c r="T186" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winedup.tw/</t>
+        </is>
+      </c>
+      <c r="U186" s="2" t="inlineStr"/>
+      <c r="V186" s="2" t="inlineStr"/>
+      <c r="W186" s="2" t="inlineStr"/>
+      <c r="X186" s="2" t="inlineStr"/>
+      <c r="Y186" s="2" t="inlineStr"/>
+      <c r="Z186" s="2" t="inlineStr"/>
+      <c r="AA186" s="2" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="inlineStr">
+        <is>
+          <t>Leading Brands Wines &amp; Spirits Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>Leading Brands Wines &amp; Spirits Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="C187" s="2" t="inlineStr">
+        <is>
+          <t>13568</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="E187" s="2" t="inlineStr">
+        <is>
+          <t>Taipei</t>
+        </is>
+      </c>
+      <c r="F187" s="2" t="inlineStr">
+        <is>
+          <t>Taipei City, Zhongshan District</t>
+        </is>
+      </c>
+      <c r="G187" s="2" t="inlineStr">
+        <is>
+          <t>58 Section 3, Minquan East Road, Section 3</t>
+        </is>
+      </c>
+      <c r="H187" s="2" t="inlineStr">
+        <is>
+          <t>10491</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>http://www.leading-brands.com.tw</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="inlineStr"/>
+      <c r="K187" s="2" t="inlineStr"/>
+      <c r="L187" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M187" s="2" t="inlineStr"/>
+      <c r="N187" s="2" t="inlineStr">
+        <is>
+          <t>order@leading-brands.com.tw</t>
+        </is>
+      </c>
+      <c r="O187" s="2" t="inlineStr">
+        <is>
+          <t>+886 2 2507 2558</t>
+        </is>
+      </c>
+      <c r="P187" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q187" s="2" t="inlineStr">
+        <is>
+          <t>27341945</t>
+        </is>
+      </c>
+      <c r="R187" s="2" t="inlineStr"/>
+      <c r="S187" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LeadingBrandsWineSpirits</t>
+        </is>
+      </c>
+      <c r="T187" s="2" t="inlineStr"/>
+      <c r="U187" s="2" t="inlineStr"/>
+      <c r="V187" s="2" t="inlineStr"/>
+      <c r="W187" s="2" t="inlineStr">
+        <is>
+          <t>Huang Sammy</t>
+        </is>
+      </c>
+      <c r="X187" s="2" t="inlineStr">
+        <is>
+          <t>Import Division</t>
+        </is>
+      </c>
+      <c r="Y187" s="2" t="inlineStr"/>
+      <c r="Z187" s="2" t="inlineStr"/>
+      <c r="AA187" s="2" t="inlineStr">
+        <is>
+          <t>https://tw.linkedin.com/pub/huang-sammy/34/107/983/en</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
